--- a/merged_products_final.xlsx
+++ b/merged_products_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA 2nd sem\TrustCart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5A12389-7D78-46FD-AF9A-38C11E4B7642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CEE5D3E-A3D4-4C67-B921-F7E01E6DEB6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2328,7 +2328,7 @@
   <dimension ref="A1:M762"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="1" max="1" width="37.109375" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
